--- a/public/plantilla-charla-diaria.xlsx
+++ b/public/plantilla-charla-diaria.xlsx
@@ -1999,7 +1999,7 @@
     <row r="74" ht="17" customHeight="1">
       <c r="A74" s="8" t="inlineStr">
         <is>
-          <t>6. EVIDENCIA FOTOGRÁFICA (opcional)</t>
+          <t>6. EVIDENCIA FOTOGRÁFICA (opcional · hasta 4 fotos)</t>
         </is>
       </c>
       <c r="B74" s="8" t="n"/>
@@ -2286,7 +2286,7 @@
       </c>
     </row>
   </sheetData>
-  <mergeCells count="263">
+  <mergeCells count="267">
     <mergeCell ref="B42:D42"/>
     <mergeCell ref="K49:L49"/>
     <mergeCell ref="B60:D60"/>
@@ -2308,6 +2308,7 @@
     <mergeCell ref="G24:I24"/>
     <mergeCell ref="J25:L25"/>
     <mergeCell ref="E51:F51"/>
+    <mergeCell ref="J85:L85"/>
     <mergeCell ref="A7:B7"/>
     <mergeCell ref="A23:C23"/>
     <mergeCell ref="A90:B90"/>
@@ -2329,9 +2330,10 @@
     <mergeCell ref="K67:L67"/>
     <mergeCell ref="D23:F23"/>
     <mergeCell ref="G68:H68"/>
-    <mergeCell ref="C88:F88"/>
+    <mergeCell ref="G75:I84"/>
     <mergeCell ref="K2:L2"/>
     <mergeCell ref="I42:J42"/>
+    <mergeCell ref="C88:F88"/>
     <mergeCell ref="E49:F49"/>
     <mergeCell ref="K42:L42"/>
     <mergeCell ref="G58:H58"/>
@@ -2359,10 +2361,10 @@
     <mergeCell ref="J24:L24"/>
     <mergeCell ref="A28:B30"/>
     <mergeCell ref="E55:F55"/>
-    <mergeCell ref="A75:F84"/>
     <mergeCell ref="I46:J46"/>
     <mergeCell ref="A11:B11"/>
     <mergeCell ref="E67:F67"/>
+    <mergeCell ref="D75:F84"/>
     <mergeCell ref="G67:H67"/>
     <mergeCell ref="G61:H61"/>
     <mergeCell ref="J26:L26"/>
@@ -2378,9 +2380,9 @@
     <mergeCell ref="D1:I2"/>
     <mergeCell ref="I57:J57"/>
     <mergeCell ref="K51:L51"/>
-    <mergeCell ref="A85:F85"/>
     <mergeCell ref="I54:J54"/>
     <mergeCell ref="A32:C32"/>
+    <mergeCell ref="J75:L84"/>
     <mergeCell ref="I72:J72"/>
     <mergeCell ref="A5:L5"/>
     <mergeCell ref="A14:B17"/>
@@ -2403,6 +2405,7 @@
     <mergeCell ref="K43:L43"/>
     <mergeCell ref="B45:D45"/>
     <mergeCell ref="K62:L62"/>
+    <mergeCell ref="D85:F85"/>
     <mergeCell ref="A31:L31"/>
     <mergeCell ref="C35:L35"/>
     <mergeCell ref="G65:H65"/>
@@ -2430,6 +2433,7 @@
     <mergeCell ref="A25:C25"/>
     <mergeCell ref="E50:F50"/>
     <mergeCell ref="K68:L68"/>
+    <mergeCell ref="A75:C84"/>
     <mergeCell ref="I88:L88"/>
     <mergeCell ref="E68:F68"/>
     <mergeCell ref="D32:F32"/>
@@ -2460,7 +2464,6 @@
     <mergeCell ref="D33:F33"/>
     <mergeCell ref="B51:D51"/>
     <mergeCell ref="E59:F59"/>
-    <mergeCell ref="G85:L85"/>
     <mergeCell ref="E46:F46"/>
     <mergeCell ref="G22:I22"/>
     <mergeCell ref="B63:D63"/>
@@ -2513,6 +2516,7 @@
     <mergeCell ref="B69:D69"/>
     <mergeCell ref="G33:I33"/>
     <mergeCell ref="A33:C33"/>
+    <mergeCell ref="A85:C85"/>
     <mergeCell ref="J22:L22"/>
     <mergeCell ref="A19:B20"/>
     <mergeCell ref="G53:H53"/>
@@ -2523,10 +2527,10 @@
     <mergeCell ref="B64:D64"/>
     <mergeCell ref="D24:F24"/>
     <mergeCell ref="G25:I25"/>
+    <mergeCell ref="G85:I85"/>
     <mergeCell ref="K59:L59"/>
     <mergeCell ref="I68:J68"/>
     <mergeCell ref="I55:J55"/>
-    <mergeCell ref="G75:L84"/>
     <mergeCell ref="J23:L23"/>
     <mergeCell ref="E45:F45"/>
     <mergeCell ref="I67:J67"/>

--- a/public/plantilla-charla-diaria.xlsx
+++ b/public/plantilla-charla-diaria.xlsx
@@ -581,7 +581,6 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:L91"/>

--- a/public/plantilla-charla-diaria.xlsx
+++ b/public/plantilla-charla-diaria.xlsx
@@ -3,7 +3,7 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <bookViews>
-    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="600" firstSheet="0" autoFilterDateGrouping="1"/>
+    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Charla Diaria" sheetId="1" state="visible" r:id="rId1"/>
@@ -15,7 +15,8 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <fonts count="39">
+  <numFmts count="0"/>
+  <fonts count="41">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -297,6 +298,15 @@
       <sz val="9"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <name val="Calibri"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <color rgb="FFFFFFFF"/>
+      <sz val="10"/>
+    </font>
   </fonts>
   <fills count="20">
     <fill>
@@ -1024,7 +1034,7 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="360">
+  <cellXfs count="378">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="3"/>
@@ -1928,6 +1938,64 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="27" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="10" fillId="6" borderId="7" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="39" fillId="0" borderId="7" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="3">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+      <protection locked="0" hidden="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="17" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <protection locked="0" hidden="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <protection locked="0" hidden="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="39" fillId="0" borderId="7" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="3">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection locked="0" hidden="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="39" fillId="0" borderId="14" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="39" fillId="0" borderId="7" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="39" fillId="0" borderId="14" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="39" fillId="0" borderId="14" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="3">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+      <protection locked="0" hidden="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <protection locked="0" hidden="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="16" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <protection locked="0" hidden="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="39" fillId="0" borderId="7" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="40" fillId="7" borderId="7" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="3">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0" hidden="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <protection locked="0" hidden="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="10" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <protection locked="0" hidden="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <protection locked="0" hidden="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <protection locked="0" hidden="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <protection locked="0" hidden="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <protection locked="0" hidden="0"/>
     </xf>
   </cellXfs>
   <cellStyles count="6">
@@ -2439,9 +2507,17 @@
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.6640625" defaultRowHeight="14.4"/>
   <cols>
     <col width="12.77734375" customWidth="1" style="2" min="1" max="2"/>
+    <col width="13" customWidth="1" style="127" min="2" max="2"/>
     <col width="13" customWidth="1" style="2" min="3" max="3"/>
     <col width="15.77734375" customWidth="1" style="2" min="4" max="10"/>
+    <col width="13" customWidth="1" style="127" min="5" max="5"/>
+    <col width="13" customWidth="1" style="127" min="6" max="6"/>
+    <col width="13" customWidth="1" style="127" min="7" max="7"/>
+    <col width="13" customWidth="1" style="127" min="8" max="8"/>
+    <col width="13" customWidth="1" style="127" min="9" max="9"/>
+    <col width="13" customWidth="1" style="127" min="10" max="10"/>
     <col width="12" customWidth="1" style="2" min="11" max="12"/>
+    <col width="13" customWidth="1" style="127" min="12" max="12"/>
     <col width="8.6640625" customWidth="1" style="2" min="13" max="16384"/>
   </cols>
   <sheetData>
@@ -2614,20 +2690,20 @@
         </is>
       </c>
       <c r="B12" s="89" t="n"/>
-      <c r="C12" s="68" t="n"/>
-      <c r="D12" s="93" t="n"/>
-      <c r="E12" s="93" t="n"/>
-      <c r="F12" s="93" t="n"/>
-      <c r="G12" s="89" t="n"/>
+      <c r="C12" s="360" t="n"/>
+      <c r="D12" s="361" t="n"/>
+      <c r="E12" s="361" t="n"/>
+      <c r="F12" s="361" t="n"/>
+      <c r="G12" s="362" t="n"/>
       <c r="H12" s="59" t="inlineStr">
         <is>
           <t>Ubicación</t>
         </is>
       </c>
       <c r="I12" s="89" t="n"/>
-      <c r="J12" s="68" t="n"/>
-      <c r="K12" s="93" t="n"/>
-      <c r="L12" s="89" t="n"/>
+      <c r="J12" s="360" t="n"/>
+      <c r="K12" s="361" t="n"/>
+      <c r="L12" s="362" t="n"/>
     </row>
     <row r="13" ht="15" customHeight="1" s="127">
       <c r="A13" s="59" t="inlineStr">
@@ -2636,32 +2712,32 @@
         </is>
       </c>
       <c r="B13" s="89" t="n"/>
-      <c r="C13" s="69" t="n"/>
+      <c r="C13" s="363" t="n"/>
       <c r="D13" s="59" t="inlineStr">
         <is>
           <t>Hora inicio</t>
         </is>
       </c>
-      <c r="E13" s="69" t="n"/>
+      <c r="E13" s="363" t="n"/>
       <c r="F13" s="59" t="inlineStr">
         <is>
           <t>Hora fin</t>
         </is>
       </c>
-      <c r="G13" s="69" t="n"/>
+      <c r="G13" s="363" t="n"/>
       <c r="H13" s="59" t="inlineStr">
         <is>
           <t>Duración</t>
         </is>
       </c>
-      <c r="I13" s="69" t="n"/>
+      <c r="I13" s="363" t="n"/>
       <c r="J13" s="59" t="inlineStr">
         <is>
           <t>N° charla</t>
         </is>
       </c>
-      <c r="K13" s="69" t="n"/>
-      <c r="L13" s="89" t="n"/>
+      <c r="K13" s="363" t="n"/>
+      <c r="L13" s="362" t="n"/>
     </row>
     <row r="14" ht="15" customHeight="1" s="127">
       <c r="A14" s="59" t="inlineStr">
@@ -2670,20 +2746,20 @@
         </is>
       </c>
       <c r="B14" s="89" t="n"/>
-      <c r="C14" s="68" t="n"/>
-      <c r="D14" s="93" t="n"/>
-      <c r="E14" s="93" t="n"/>
-      <c r="F14" s="93" t="n"/>
-      <c r="G14" s="89" t="n"/>
+      <c r="C14" s="360" t="n"/>
+      <c r="D14" s="361" t="n"/>
+      <c r="E14" s="361" t="n"/>
+      <c r="F14" s="361" t="n"/>
+      <c r="G14" s="362" t="n"/>
       <c r="H14" s="59" t="inlineStr">
         <is>
           <t>Tipo de charla</t>
         </is>
       </c>
       <c r="I14" s="89" t="n"/>
-      <c r="J14" s="68" t="n"/>
-      <c r="K14" s="93" t="n"/>
-      <c r="L14" s="89" t="n"/>
+      <c r="J14" s="360" t="n"/>
+      <c r="K14" s="361" t="n"/>
+      <c r="L14" s="362" t="n"/>
     </row>
     <row r="15" ht="15" customHeight="1" s="127">
       <c r="A15" s="59" t="inlineStr">
@@ -2692,20 +2768,20 @@
         </is>
       </c>
       <c r="B15" s="89" t="n"/>
-      <c r="C15" s="68" t="n"/>
-      <c r="D15" s="93" t="n"/>
-      <c r="E15" s="93" t="n"/>
-      <c r="F15" s="93" t="n"/>
-      <c r="G15" s="89" t="n"/>
+      <c r="C15" s="360" t="n"/>
+      <c r="D15" s="361" t="n"/>
+      <c r="E15" s="361" t="n"/>
+      <c r="F15" s="361" t="n"/>
+      <c r="G15" s="362" t="n"/>
       <c r="H15" s="59" t="inlineStr">
         <is>
           <t>Cargo</t>
         </is>
       </c>
       <c r="I15" s="89" t="n"/>
-      <c r="J15" s="68" t="n"/>
-      <c r="K15" s="93" t="n"/>
-      <c r="L15" s="89" t="n"/>
+      <c r="J15" s="360" t="n"/>
+      <c r="K15" s="361" t="n"/>
+      <c r="L15" s="362" t="n"/>
     </row>
     <row r="16" ht="16.5" customHeight="1" s="127">
       <c r="A16" s="215" t="inlineStr">
@@ -2732,16 +2808,16 @@
         </is>
       </c>
       <c r="B17" s="89" t="n"/>
-      <c r="C17" s="68" t="n"/>
-      <c r="D17" s="93" t="n"/>
-      <c r="E17" s="93" t="n"/>
-      <c r="F17" s="93" t="n"/>
-      <c r="G17" s="93" t="n"/>
-      <c r="H17" s="93" t="n"/>
-      <c r="I17" s="93" t="n"/>
-      <c r="J17" s="93" t="n"/>
-      <c r="K17" s="93" t="n"/>
-      <c r="L17" s="89" t="n"/>
+      <c r="C17" s="360" t="n"/>
+      <c r="D17" s="361" t="n"/>
+      <c r="E17" s="361" t="n"/>
+      <c r="F17" s="361" t="n"/>
+      <c r="G17" s="361" t="n"/>
+      <c r="H17" s="361" t="n"/>
+      <c r="I17" s="361" t="n"/>
+      <c r="J17" s="361" t="n"/>
+      <c r="K17" s="361" t="n"/>
+      <c r="L17" s="362" t="n"/>
     </row>
     <row r="18" ht="24" customHeight="1" s="127">
       <c r="A18" s="59" t="inlineStr">
@@ -2856,28 +2932,28 @@
       <c r="L25" s="350" t="n"/>
     </row>
     <row r="26" ht="19.5" customHeight="1" s="127">
-      <c r="A26" s="230" t="inlineStr">
+      <c r="A26" s="364" t="inlineStr">
         <is>
           <t>☐ Caída a distinto nivel (alturas)</t>
         </is>
       </c>
       <c r="B26" s="98" t="n"/>
       <c r="C26" s="97" t="n"/>
-      <c r="D26" s="230" t="inlineStr">
+      <c r="D26" s="364" t="inlineStr">
         <is>
           <t>☐ Caída al mismo nivel / resbalones</t>
         </is>
       </c>
       <c r="E26" s="98" t="n"/>
       <c r="F26" s="97" t="n"/>
-      <c r="G26" s="230" t="inlineStr">
+      <c r="G26" s="364" t="inlineStr">
         <is>
           <t>☐ Caída de objetos o herramientas</t>
         </is>
       </c>
       <c r="H26" s="98" t="n"/>
       <c r="I26" s="97" t="n"/>
-      <c r="J26" s="230" t="inlineStr">
+      <c r="J26" s="364" t="inlineStr">
         <is>
           <t>☐ Golpes, cortes y atrapamientos</t>
         </is>
@@ -2886,28 +2962,28 @@
       <c r="L26" s="97" t="n"/>
     </row>
     <row r="27" ht="19.5" customHeight="1" s="127">
-      <c r="A27" s="72" t="inlineStr">
+      <c r="A27" s="365" t="inlineStr">
         <is>
           <t>☐ Sobreesfuerzo / carga manual</t>
         </is>
       </c>
       <c r="B27" s="93" t="n"/>
       <c r="C27" s="89" t="n"/>
-      <c r="D27" s="72" t="inlineStr">
+      <c r="D27" s="365" t="inlineStr">
         <is>
           <t>☐ Riesgo eléctrico</t>
         </is>
       </c>
       <c r="E27" s="93" t="n"/>
       <c r="F27" s="89" t="n"/>
-      <c r="G27" s="72" t="inlineStr">
+      <c r="G27" s="365" t="inlineStr">
         <is>
           <t>☐ Proyección de partículas</t>
         </is>
       </c>
       <c r="H27" s="93" t="n"/>
       <c r="I27" s="89" t="n"/>
-      <c r="J27" s="72" t="inlineStr">
+      <c r="J27" s="365" t="inlineStr">
         <is>
           <t>☐ Ruido</t>
         </is>
@@ -2916,28 +2992,28 @@
       <c r="L27" s="89" t="n"/>
     </row>
     <row r="28" ht="19.5" customHeight="1" s="127">
-      <c r="A28" s="72" t="inlineStr">
+      <c r="A28" s="365" t="inlineStr">
         <is>
           <t>☐ Polvo / material particulado</t>
         </is>
       </c>
       <c r="B28" s="93" t="n"/>
       <c r="C28" s="89" t="n"/>
-      <c r="D28" s="72" t="inlineStr">
+      <c r="D28" s="365" t="inlineStr">
         <is>
           <t>☐ Tránsito de vehículos y maquinaria</t>
         </is>
       </c>
       <c r="E28" s="93" t="n"/>
       <c r="F28" s="89" t="n"/>
-      <c r="G28" s="72" t="inlineStr">
+      <c r="G28" s="365" t="inlineStr">
         <is>
           <t>☐ Excavaciones / taludes</t>
         </is>
       </c>
       <c r="H28" s="93" t="n"/>
       <c r="I28" s="89" t="n"/>
-      <c r="J28" s="72" t="inlineStr">
+      <c r="J28" s="365" t="inlineStr">
         <is>
           <t>☐ Izaje de cargas</t>
         </is>
@@ -2946,28 +3022,28 @@
       <c r="L28" s="89" t="n"/>
     </row>
     <row r="29" ht="19.5" customHeight="1" s="127">
-      <c r="A29" s="72" t="inlineStr">
+      <c r="A29" s="365" t="inlineStr">
         <is>
           <t>☐ Trabajo en caliente / incendio</t>
         </is>
       </c>
       <c r="B29" s="93" t="n"/>
       <c r="C29" s="89" t="n"/>
-      <c r="D29" s="72" t="inlineStr">
+      <c r="D29" s="365" t="inlineStr">
         <is>
           <t>☐ Espacios confinados / gases</t>
         </is>
       </c>
       <c r="E29" s="93" t="n"/>
       <c r="F29" s="89" t="n"/>
-      <c r="G29" s="72" t="inlineStr">
+      <c r="G29" s="365" t="inlineStr">
         <is>
           <t>☐ Sustancias químicas / derrames</t>
         </is>
       </c>
       <c r="H29" s="93" t="n"/>
       <c r="I29" s="89" t="n"/>
-      <c r="J29" s="72" t="inlineStr">
+      <c r="J29" s="365" t="inlineStr">
         <is>
           <t>☐ Exposición solar / calor</t>
         </is>
@@ -2976,28 +3052,28 @@
       <c r="L29" s="89" t="n"/>
     </row>
     <row r="30" ht="19.5" customHeight="1" s="127">
-      <c r="A30" s="72" t="inlineStr">
+      <c r="A30" s="365" t="inlineStr">
         <is>
           <t>☐ Lluvia / tormenta eléctrica</t>
         </is>
       </c>
       <c r="B30" s="93" t="n"/>
       <c r="C30" s="89" t="n"/>
-      <c r="D30" s="72" t="inlineStr">
+      <c r="D30" s="365" t="inlineStr">
         <is>
           <t>☐ Animales (serpientes, insectos)</t>
         </is>
       </c>
       <c r="E30" s="93" t="n"/>
       <c r="F30" s="89" t="n"/>
-      <c r="G30" s="72" t="inlineStr">
+      <c r="G30" s="365" t="inlineStr">
         <is>
           <t>☐ Seguridad pública / terceros</t>
         </is>
       </c>
       <c r="H30" s="93" t="n"/>
       <c r="I30" s="89" t="n"/>
-      <c r="J30" s="72" t="inlineStr">
+      <c r="J30" s="365" t="inlineStr">
         <is>
           <t>☐ Orden y aseo deficiente</t>
         </is>
@@ -3080,28 +3156,28 @@
       <c r="L35" s="350" t="n"/>
     </row>
     <row r="36" ht="19.5" customHeight="1" s="127">
-      <c r="A36" s="230" t="inlineStr">
+      <c r="A36" s="364" t="inlineStr">
         <is>
           <t>☐ Casco de seguridad</t>
         </is>
       </c>
       <c r="B36" s="98" t="n"/>
       <c r="C36" s="97" t="n"/>
-      <c r="D36" s="230" t="inlineStr">
+      <c r="D36" s="364" t="inlineStr">
         <is>
           <t>☐ Gafas de seguridad</t>
         </is>
       </c>
       <c r="E36" s="98" t="n"/>
       <c r="F36" s="97" t="n"/>
-      <c r="G36" s="230" t="inlineStr">
+      <c r="G36" s="364" t="inlineStr">
         <is>
           <t>☐ Guantes</t>
         </is>
       </c>
       <c r="H36" s="98" t="n"/>
       <c r="I36" s="97" t="n"/>
-      <c r="J36" s="230" t="inlineStr">
+      <c r="J36" s="364" t="inlineStr">
         <is>
           <t>☐ Botas de seguridad</t>
         </is>
@@ -3110,28 +3186,28 @@
       <c r="L36" s="97" t="n"/>
     </row>
     <row r="37" ht="19.5" customHeight="1" s="127">
-      <c r="A37" s="72" t="inlineStr">
+      <c r="A37" s="365" t="inlineStr">
         <is>
           <t>☐ Arnés y línea de vida</t>
         </is>
       </c>
       <c r="B37" s="93" t="n"/>
       <c r="C37" s="89" t="n"/>
-      <c r="D37" s="72" t="inlineStr">
+      <c r="D37" s="365" t="inlineStr">
         <is>
           <t>☐ Protección auditiva</t>
         </is>
       </c>
       <c r="E37" s="93" t="n"/>
       <c r="F37" s="89" t="n"/>
-      <c r="G37" s="72" t="inlineStr">
+      <c r="G37" s="365" t="inlineStr">
         <is>
           <t>☐ Respirador / mascarilla</t>
         </is>
       </c>
       <c r="H37" s="93" t="n"/>
       <c r="I37" s="89" t="n"/>
-      <c r="J37" s="72" t="inlineStr">
+      <c r="J37" s="365" t="inlineStr">
         <is>
           <t>☐ Chaleco reflectivo</t>
         </is>
@@ -3140,28 +3216,28 @@
       <c r="L37" s="89" t="n"/>
     </row>
     <row r="38" ht="19.5" customHeight="1" s="127">
-      <c r="A38" s="72" t="inlineStr">
+      <c r="A38" s="365" t="inlineStr">
         <is>
           <t>☐ Careta / protector facial</t>
         </is>
       </c>
       <c r="B38" s="93" t="n"/>
       <c r="C38" s="89" t="n"/>
-      <c r="D38" s="72" t="inlineStr">
+      <c r="D38" s="365" t="inlineStr">
         <is>
           <t>☐ Overol / ropa de trabajo</t>
         </is>
       </c>
       <c r="E38" s="93" t="n"/>
       <c r="F38" s="89" t="n"/>
-      <c r="G38" s="72" t="inlineStr">
+      <c r="G38" s="365" t="inlineStr">
         <is>
           <t>☐ Impermeable (lluvia)</t>
         </is>
       </c>
       <c r="H38" s="93" t="n"/>
       <c r="I38" s="89" t="n"/>
-      <c r="J38" s="72" t="inlineStr">
+      <c r="J38" s="365" t="inlineStr">
         <is>
           <t>☐ Protector solar / hidratación</t>
         </is>
@@ -3212,24 +3288,24 @@
         </is>
       </c>
       <c r="B41" s="89" t="n"/>
-      <c r="C41" s="69" t="n"/>
-      <c r="D41" s="89" t="n"/>
+      <c r="C41" s="363" t="n"/>
+      <c r="D41" s="362" t="n"/>
       <c r="E41" s="169" t="inlineStr">
         <is>
           <t>Orden y aseo del área</t>
         </is>
       </c>
       <c r="F41" s="89" t="n"/>
-      <c r="G41" s="75" t="n"/>
-      <c r="H41" s="89" t="n"/>
+      <c r="G41" s="363" t="n"/>
+      <c r="H41" s="362" t="n"/>
       <c r="I41" s="169" t="inlineStr">
         <is>
           <t>Personal con síntomas / no apto</t>
         </is>
       </c>
       <c r="J41" s="89" t="n"/>
-      <c r="K41" s="75" t="n"/>
-      <c r="L41" s="89" t="n"/>
+      <c r="K41" s="363" t="n"/>
+      <c r="L41" s="362" t="n"/>
     </row>
     <row r="42" ht="25.5" customHeight="1" s="127">
       <c r="A42" s="169" t="inlineStr">
@@ -3326,484 +3402,484 @@
       <c r="L46" s="348" t="n"/>
     </row>
     <row r="47" ht="18" customHeight="1" s="127">
-      <c r="A47" s="306" t="n">
+      <c r="A47" s="366" t="n">
         <v>1</v>
       </c>
-      <c r="B47" s="315" t="n"/>
-      <c r="C47" s="98" t="n"/>
-      <c r="D47" s="97" t="n"/>
-      <c r="E47" s="315" t="n"/>
-      <c r="F47" s="97" t="n"/>
-      <c r="G47" s="315" t="n"/>
-      <c r="H47" s="97" t="n"/>
-      <c r="I47" s="315" t="n"/>
-      <c r="J47" s="97" t="n"/>
-      <c r="K47" s="315" t="n"/>
-      <c r="L47" s="97" t="n"/>
+      <c r="B47" s="367" t="n"/>
+      <c r="C47" s="368" t="n"/>
+      <c r="D47" s="369" t="n"/>
+      <c r="E47" s="367" t="n"/>
+      <c r="F47" s="369" t="n"/>
+      <c r="G47" s="367" t="n"/>
+      <c r="H47" s="369" t="n"/>
+      <c r="I47" s="367" t="n"/>
+      <c r="J47" s="369" t="n"/>
+      <c r="K47" s="367" t="n"/>
+      <c r="L47" s="369" t="n"/>
     </row>
     <row r="48" ht="18" customHeight="1" s="127">
-      <c r="A48" s="126" t="n">
+      <c r="A48" s="370" t="n">
         <v>2</v>
       </c>
-      <c r="B48" s="76" t="n"/>
-      <c r="C48" s="93" t="n"/>
-      <c r="D48" s="89" t="n"/>
-      <c r="E48" s="76" t="n"/>
-      <c r="F48" s="89" t="n"/>
-      <c r="G48" s="76" t="n"/>
-      <c r="H48" s="89" t="n"/>
-      <c r="I48" s="76" t="n"/>
-      <c r="J48" s="89" t="n"/>
-      <c r="K48" s="76" t="n"/>
-      <c r="L48" s="89" t="n"/>
+      <c r="B48" s="360" t="n"/>
+      <c r="C48" s="361" t="n"/>
+      <c r="D48" s="362" t="n"/>
+      <c r="E48" s="360" t="n"/>
+      <c r="F48" s="362" t="n"/>
+      <c r="G48" s="360" t="n"/>
+      <c r="H48" s="362" t="n"/>
+      <c r="I48" s="360" t="n"/>
+      <c r="J48" s="362" t="n"/>
+      <c r="K48" s="360" t="n"/>
+      <c r="L48" s="362" t="n"/>
     </row>
     <row r="49" ht="18" customHeight="1" s="127">
-      <c r="A49" s="126" t="n">
+      <c r="A49" s="370" t="n">
         <v>3</v>
       </c>
-      <c r="B49" s="76" t="n"/>
-      <c r="C49" s="93" t="n"/>
-      <c r="D49" s="89" t="n"/>
-      <c r="E49" s="76" t="n"/>
-      <c r="F49" s="89" t="n"/>
-      <c r="G49" s="76" t="n"/>
-      <c r="H49" s="89" t="n"/>
-      <c r="I49" s="76" t="n"/>
-      <c r="J49" s="89" t="n"/>
-      <c r="K49" s="76" t="n"/>
-      <c r="L49" s="89" t="n"/>
+      <c r="B49" s="360" t="n"/>
+      <c r="C49" s="361" t="n"/>
+      <c r="D49" s="362" t="n"/>
+      <c r="E49" s="360" t="n"/>
+      <c r="F49" s="362" t="n"/>
+      <c r="G49" s="360" t="n"/>
+      <c r="H49" s="362" t="n"/>
+      <c r="I49" s="360" t="n"/>
+      <c r="J49" s="362" t="n"/>
+      <c r="K49" s="360" t="n"/>
+      <c r="L49" s="362" t="n"/>
     </row>
     <row r="50" ht="18" customHeight="1" s="127">
-      <c r="A50" s="126" t="n">
+      <c r="A50" s="370" t="n">
         <v>4</v>
       </c>
-      <c r="B50" s="76" t="n"/>
-      <c r="C50" s="93" t="n"/>
-      <c r="D50" s="89" t="n"/>
-      <c r="E50" s="76" t="n"/>
-      <c r="F50" s="89" t="n"/>
-      <c r="G50" s="76" t="n"/>
-      <c r="H50" s="89" t="n"/>
-      <c r="I50" s="76" t="n"/>
-      <c r="J50" s="89" t="n"/>
-      <c r="K50" s="76" t="n"/>
-      <c r="L50" s="89" t="n"/>
+      <c r="B50" s="360" t="n"/>
+      <c r="C50" s="361" t="n"/>
+      <c r="D50" s="362" t="n"/>
+      <c r="E50" s="360" t="n"/>
+      <c r="F50" s="362" t="n"/>
+      <c r="G50" s="360" t="n"/>
+      <c r="H50" s="362" t="n"/>
+      <c r="I50" s="360" t="n"/>
+      <c r="J50" s="362" t="n"/>
+      <c r="K50" s="360" t="n"/>
+      <c r="L50" s="362" t="n"/>
     </row>
     <row r="51" ht="18" customHeight="1" s="127">
-      <c r="A51" s="126" t="n">
+      <c r="A51" s="370" t="n">
         <v>5</v>
       </c>
-      <c r="B51" s="76" t="n"/>
-      <c r="C51" s="93" t="n"/>
-      <c r="D51" s="89" t="n"/>
-      <c r="E51" s="76" t="n"/>
-      <c r="F51" s="89" t="n"/>
-      <c r="G51" s="76" t="n"/>
-      <c r="H51" s="89" t="n"/>
-      <c r="I51" s="76" t="n"/>
-      <c r="J51" s="89" t="n"/>
-      <c r="K51" s="76" t="n"/>
-      <c r="L51" s="89" t="n"/>
+      <c r="B51" s="360" t="n"/>
+      <c r="C51" s="361" t="n"/>
+      <c r="D51" s="362" t="n"/>
+      <c r="E51" s="360" t="n"/>
+      <c r="F51" s="362" t="n"/>
+      <c r="G51" s="360" t="n"/>
+      <c r="H51" s="362" t="n"/>
+      <c r="I51" s="360" t="n"/>
+      <c r="J51" s="362" t="n"/>
+      <c r="K51" s="360" t="n"/>
+      <c r="L51" s="362" t="n"/>
     </row>
     <row r="52" ht="18" customHeight="1" s="127">
-      <c r="A52" s="126" t="n">
+      <c r="A52" s="370" t="n">
         <v>6</v>
       </c>
-      <c r="B52" s="76" t="n"/>
-      <c r="C52" s="93" t="n"/>
-      <c r="D52" s="89" t="n"/>
-      <c r="E52" s="76" t="n"/>
-      <c r="F52" s="89" t="n"/>
-      <c r="G52" s="76" t="n"/>
-      <c r="H52" s="89" t="n"/>
-      <c r="I52" s="76" t="n"/>
-      <c r="J52" s="89" t="n"/>
-      <c r="K52" s="76" t="n"/>
-      <c r="L52" s="89" t="n"/>
+      <c r="B52" s="360" t="n"/>
+      <c r="C52" s="361" t="n"/>
+      <c r="D52" s="362" t="n"/>
+      <c r="E52" s="360" t="n"/>
+      <c r="F52" s="362" t="n"/>
+      <c r="G52" s="360" t="n"/>
+      <c r="H52" s="362" t="n"/>
+      <c r="I52" s="360" t="n"/>
+      <c r="J52" s="362" t="n"/>
+      <c r="K52" s="360" t="n"/>
+      <c r="L52" s="362" t="n"/>
     </row>
     <row r="53" ht="18" customHeight="1" s="127">
-      <c r="A53" s="126" t="n">
+      <c r="A53" s="370" t="n">
         <v>7</v>
       </c>
-      <c r="B53" s="76" t="n"/>
-      <c r="C53" s="93" t="n"/>
-      <c r="D53" s="89" t="n"/>
-      <c r="E53" s="76" t="n"/>
-      <c r="F53" s="89" t="n"/>
-      <c r="G53" s="76" t="n"/>
-      <c r="H53" s="89" t="n"/>
-      <c r="I53" s="76" t="n"/>
-      <c r="J53" s="89" t="n"/>
-      <c r="K53" s="76" t="n"/>
-      <c r="L53" s="89" t="n"/>
+      <c r="B53" s="360" t="n"/>
+      <c r="C53" s="361" t="n"/>
+      <c r="D53" s="362" t="n"/>
+      <c r="E53" s="360" t="n"/>
+      <c r="F53" s="362" t="n"/>
+      <c r="G53" s="360" t="n"/>
+      <c r="H53" s="362" t="n"/>
+      <c r="I53" s="360" t="n"/>
+      <c r="J53" s="362" t="n"/>
+      <c r="K53" s="360" t="n"/>
+      <c r="L53" s="362" t="n"/>
     </row>
     <row r="54" ht="18" customHeight="1" s="127">
-      <c r="A54" s="126" t="n">
+      <c r="A54" s="370" t="n">
         <v>8</v>
       </c>
-      <c r="B54" s="76" t="n"/>
-      <c r="C54" s="93" t="n"/>
-      <c r="D54" s="89" t="n"/>
-      <c r="E54" s="76" t="n"/>
-      <c r="F54" s="89" t="n"/>
-      <c r="G54" s="76" t="n"/>
-      <c r="H54" s="89" t="n"/>
-      <c r="I54" s="76" t="n"/>
-      <c r="J54" s="89" t="n"/>
-      <c r="K54" s="76" t="n"/>
-      <c r="L54" s="89" t="n"/>
+      <c r="B54" s="360" t="n"/>
+      <c r="C54" s="361" t="n"/>
+      <c r="D54" s="362" t="n"/>
+      <c r="E54" s="360" t="n"/>
+      <c r="F54" s="362" t="n"/>
+      <c r="G54" s="360" t="n"/>
+      <c r="H54" s="362" t="n"/>
+      <c r="I54" s="360" t="n"/>
+      <c r="J54" s="362" t="n"/>
+      <c r="K54" s="360" t="n"/>
+      <c r="L54" s="362" t="n"/>
     </row>
     <row r="55" ht="18" customHeight="1" s="127">
-      <c r="A55" s="126" t="n">
+      <c r="A55" s="370" t="n">
         <v>9</v>
       </c>
-      <c r="B55" s="76" t="n"/>
-      <c r="C55" s="93" t="n"/>
-      <c r="D55" s="89" t="n"/>
-      <c r="E55" s="76" t="n"/>
-      <c r="F55" s="89" t="n"/>
-      <c r="G55" s="76" t="n"/>
-      <c r="H55" s="89" t="n"/>
-      <c r="I55" s="76" t="n"/>
-      <c r="J55" s="89" t="n"/>
-      <c r="K55" s="76" t="n"/>
-      <c r="L55" s="89" t="n"/>
+      <c r="B55" s="360" t="n"/>
+      <c r="C55" s="361" t="n"/>
+      <c r="D55" s="362" t="n"/>
+      <c r="E55" s="360" t="n"/>
+      <c r="F55" s="362" t="n"/>
+      <c r="G55" s="360" t="n"/>
+      <c r="H55" s="362" t="n"/>
+      <c r="I55" s="360" t="n"/>
+      <c r="J55" s="362" t="n"/>
+      <c r="K55" s="360" t="n"/>
+      <c r="L55" s="362" t="n"/>
     </row>
     <row r="56" ht="18" customHeight="1" s="127">
-      <c r="A56" s="126" t="n">
+      <c r="A56" s="370" t="n">
         <v>10</v>
       </c>
-      <c r="B56" s="76" t="n"/>
-      <c r="C56" s="93" t="n"/>
-      <c r="D56" s="89" t="n"/>
-      <c r="E56" s="76" t="n"/>
-      <c r="F56" s="89" t="n"/>
-      <c r="G56" s="76" t="n"/>
-      <c r="H56" s="89" t="n"/>
-      <c r="I56" s="76" t="n"/>
-      <c r="J56" s="89" t="n"/>
-      <c r="K56" s="76" t="n"/>
-      <c r="L56" s="89" t="n"/>
+      <c r="B56" s="360" t="n"/>
+      <c r="C56" s="361" t="n"/>
+      <c r="D56" s="362" t="n"/>
+      <c r="E56" s="360" t="n"/>
+      <c r="F56" s="362" t="n"/>
+      <c r="G56" s="360" t="n"/>
+      <c r="H56" s="362" t="n"/>
+      <c r="I56" s="360" t="n"/>
+      <c r="J56" s="362" t="n"/>
+      <c r="K56" s="360" t="n"/>
+      <c r="L56" s="362" t="n"/>
     </row>
     <row r="57" ht="18" customHeight="1" s="127">
-      <c r="A57" s="126" t="n">
+      <c r="A57" s="370" t="n">
         <v>11</v>
       </c>
-      <c r="B57" s="76" t="n"/>
-      <c r="C57" s="93" t="n"/>
-      <c r="D57" s="89" t="n"/>
-      <c r="E57" s="76" t="n"/>
-      <c r="F57" s="89" t="n"/>
-      <c r="G57" s="76" t="n"/>
-      <c r="H57" s="89" t="n"/>
-      <c r="I57" s="76" t="n"/>
-      <c r="J57" s="89" t="n"/>
-      <c r="K57" s="76" t="n"/>
-      <c r="L57" s="89" t="n"/>
+      <c r="B57" s="360" t="n"/>
+      <c r="C57" s="361" t="n"/>
+      <c r="D57" s="362" t="n"/>
+      <c r="E57" s="360" t="n"/>
+      <c r="F57" s="362" t="n"/>
+      <c r="G57" s="360" t="n"/>
+      <c r="H57" s="362" t="n"/>
+      <c r="I57" s="360" t="n"/>
+      <c r="J57" s="362" t="n"/>
+      <c r="K57" s="360" t="n"/>
+      <c r="L57" s="362" t="n"/>
     </row>
     <row r="58" ht="18" customHeight="1" s="127">
-      <c r="A58" s="126" t="n">
+      <c r="A58" s="370" t="n">
         <v>12</v>
       </c>
-      <c r="B58" s="76" t="n"/>
-      <c r="C58" s="93" t="n"/>
-      <c r="D58" s="89" t="n"/>
-      <c r="E58" s="76" t="n"/>
-      <c r="F58" s="89" t="n"/>
-      <c r="G58" s="76" t="n"/>
-      <c r="H58" s="89" t="n"/>
-      <c r="I58" s="76" t="n"/>
-      <c r="J58" s="89" t="n"/>
-      <c r="K58" s="76" t="n"/>
-      <c r="L58" s="89" t="n"/>
+      <c r="B58" s="360" t="n"/>
+      <c r="C58" s="361" t="n"/>
+      <c r="D58" s="362" t="n"/>
+      <c r="E58" s="360" t="n"/>
+      <c r="F58" s="362" t="n"/>
+      <c r="G58" s="360" t="n"/>
+      <c r="H58" s="362" t="n"/>
+      <c r="I58" s="360" t="n"/>
+      <c r="J58" s="362" t="n"/>
+      <c r="K58" s="360" t="n"/>
+      <c r="L58" s="362" t="n"/>
     </row>
     <row r="59" ht="18" customHeight="1" s="127">
-      <c r="A59" s="126" t="n">
+      <c r="A59" s="370" t="n">
         <v>13</v>
       </c>
-      <c r="B59" s="76" t="n"/>
-      <c r="C59" s="93" t="n"/>
-      <c r="D59" s="89" t="n"/>
-      <c r="E59" s="76" t="n"/>
-      <c r="F59" s="89" t="n"/>
-      <c r="G59" s="76" t="n"/>
-      <c r="H59" s="89" t="n"/>
-      <c r="I59" s="76" t="n"/>
-      <c r="J59" s="89" t="n"/>
-      <c r="K59" s="76" t="n"/>
-      <c r="L59" s="89" t="n"/>
+      <c r="B59" s="360" t="n"/>
+      <c r="C59" s="361" t="n"/>
+      <c r="D59" s="362" t="n"/>
+      <c r="E59" s="360" t="n"/>
+      <c r="F59" s="362" t="n"/>
+      <c r="G59" s="360" t="n"/>
+      <c r="H59" s="362" t="n"/>
+      <c r="I59" s="360" t="n"/>
+      <c r="J59" s="362" t="n"/>
+      <c r="K59" s="360" t="n"/>
+      <c r="L59" s="362" t="n"/>
     </row>
     <row r="60" ht="18" customHeight="1" s="127">
-      <c r="A60" s="126" t="n">
+      <c r="A60" s="370" t="n">
         <v>14</v>
       </c>
-      <c r="B60" s="76" t="n"/>
-      <c r="C60" s="93" t="n"/>
-      <c r="D60" s="89" t="n"/>
-      <c r="E60" s="76" t="n"/>
-      <c r="F60" s="89" t="n"/>
-      <c r="G60" s="76" t="n"/>
-      <c r="H60" s="89" t="n"/>
-      <c r="I60" s="76" t="n"/>
-      <c r="J60" s="89" t="n"/>
-      <c r="K60" s="76" t="n"/>
-      <c r="L60" s="89" t="n"/>
+      <c r="B60" s="360" t="n"/>
+      <c r="C60" s="361" t="n"/>
+      <c r="D60" s="362" t="n"/>
+      <c r="E60" s="360" t="n"/>
+      <c r="F60" s="362" t="n"/>
+      <c r="G60" s="360" t="n"/>
+      <c r="H60" s="362" t="n"/>
+      <c r="I60" s="360" t="n"/>
+      <c r="J60" s="362" t="n"/>
+      <c r="K60" s="360" t="n"/>
+      <c r="L60" s="362" t="n"/>
     </row>
     <row r="61" ht="18" customHeight="1" s="127">
-      <c r="A61" s="126" t="n">
+      <c r="A61" s="370" t="n">
         <v>15</v>
       </c>
-      <c r="B61" s="76" t="n"/>
-      <c r="C61" s="93" t="n"/>
-      <c r="D61" s="89" t="n"/>
-      <c r="E61" s="76" t="n"/>
-      <c r="F61" s="89" t="n"/>
-      <c r="G61" s="76" t="n"/>
-      <c r="H61" s="89" t="n"/>
-      <c r="I61" s="76" t="n"/>
-      <c r="J61" s="89" t="n"/>
-      <c r="K61" s="76" t="n"/>
-      <c r="L61" s="89" t="n"/>
+      <c r="B61" s="360" t="n"/>
+      <c r="C61" s="361" t="n"/>
+      <c r="D61" s="362" t="n"/>
+      <c r="E61" s="360" t="n"/>
+      <c r="F61" s="362" t="n"/>
+      <c r="G61" s="360" t="n"/>
+      <c r="H61" s="362" t="n"/>
+      <c r="I61" s="360" t="n"/>
+      <c r="J61" s="362" t="n"/>
+      <c r="K61" s="360" t="n"/>
+      <c r="L61" s="362" t="n"/>
     </row>
     <row r="62" ht="18" customHeight="1" s="127">
-      <c r="A62" s="126" t="n">
+      <c r="A62" s="370" t="n">
         <v>16</v>
       </c>
-      <c r="B62" s="76" t="n"/>
-      <c r="C62" s="93" t="n"/>
-      <c r="D62" s="89" t="n"/>
-      <c r="E62" s="76" t="n"/>
-      <c r="F62" s="89" t="n"/>
-      <c r="G62" s="76" t="n"/>
-      <c r="H62" s="89" t="n"/>
-      <c r="I62" s="76" t="n"/>
-      <c r="J62" s="89" t="n"/>
-      <c r="K62" s="76" t="n"/>
-      <c r="L62" s="89" t="n"/>
+      <c r="B62" s="360" t="n"/>
+      <c r="C62" s="361" t="n"/>
+      <c r="D62" s="362" t="n"/>
+      <c r="E62" s="360" t="n"/>
+      <c r="F62" s="362" t="n"/>
+      <c r="G62" s="360" t="n"/>
+      <c r="H62" s="362" t="n"/>
+      <c r="I62" s="360" t="n"/>
+      <c r="J62" s="362" t="n"/>
+      <c r="K62" s="360" t="n"/>
+      <c r="L62" s="362" t="n"/>
     </row>
     <row r="63" ht="18" customHeight="1" s="127">
-      <c r="A63" s="126" t="n">
+      <c r="A63" s="370" t="n">
         <v>17</v>
       </c>
-      <c r="B63" s="76" t="n"/>
-      <c r="C63" s="93" t="n"/>
-      <c r="D63" s="89" t="n"/>
-      <c r="E63" s="76" t="n"/>
-      <c r="F63" s="89" t="n"/>
-      <c r="G63" s="76" t="n"/>
-      <c r="H63" s="89" t="n"/>
-      <c r="I63" s="76" t="n"/>
-      <c r="J63" s="89" t="n"/>
-      <c r="K63" s="76" t="n"/>
-      <c r="L63" s="89" t="n"/>
+      <c r="B63" s="360" t="n"/>
+      <c r="C63" s="361" t="n"/>
+      <c r="D63" s="362" t="n"/>
+      <c r="E63" s="360" t="n"/>
+      <c r="F63" s="362" t="n"/>
+      <c r="G63" s="360" t="n"/>
+      <c r="H63" s="362" t="n"/>
+      <c r="I63" s="360" t="n"/>
+      <c r="J63" s="362" t="n"/>
+      <c r="K63" s="360" t="n"/>
+      <c r="L63" s="362" t="n"/>
     </row>
     <row r="64" ht="18" customHeight="1" s="127">
-      <c r="A64" s="126" t="n">
+      <c r="A64" s="370" t="n">
         <v>18</v>
       </c>
-      <c r="B64" s="76" t="n"/>
-      <c r="C64" s="93" t="n"/>
-      <c r="D64" s="89" t="n"/>
-      <c r="E64" s="76" t="n"/>
-      <c r="F64" s="89" t="n"/>
-      <c r="G64" s="76" t="n"/>
-      <c r="H64" s="89" t="n"/>
-      <c r="I64" s="76" t="n"/>
-      <c r="J64" s="89" t="n"/>
-      <c r="K64" s="76" t="n"/>
-      <c r="L64" s="89" t="n"/>
+      <c r="B64" s="360" t="n"/>
+      <c r="C64" s="361" t="n"/>
+      <c r="D64" s="362" t="n"/>
+      <c r="E64" s="360" t="n"/>
+      <c r="F64" s="362" t="n"/>
+      <c r="G64" s="360" t="n"/>
+      <c r="H64" s="362" t="n"/>
+      <c r="I64" s="360" t="n"/>
+      <c r="J64" s="362" t="n"/>
+      <c r="K64" s="360" t="n"/>
+      <c r="L64" s="362" t="n"/>
     </row>
     <row r="65" ht="18" customHeight="1" s="127">
-      <c r="A65" s="126" t="n">
+      <c r="A65" s="370" t="n">
         <v>19</v>
       </c>
-      <c r="B65" s="76" t="n"/>
-      <c r="C65" s="93" t="n"/>
-      <c r="D65" s="89" t="n"/>
-      <c r="E65" s="76" t="n"/>
-      <c r="F65" s="89" t="n"/>
-      <c r="G65" s="76" t="n"/>
-      <c r="H65" s="89" t="n"/>
-      <c r="I65" s="76" t="n"/>
-      <c r="J65" s="89" t="n"/>
-      <c r="K65" s="76" t="n"/>
-      <c r="L65" s="89" t="n"/>
+      <c r="B65" s="360" t="n"/>
+      <c r="C65" s="361" t="n"/>
+      <c r="D65" s="362" t="n"/>
+      <c r="E65" s="360" t="n"/>
+      <c r="F65" s="362" t="n"/>
+      <c r="G65" s="360" t="n"/>
+      <c r="H65" s="362" t="n"/>
+      <c r="I65" s="360" t="n"/>
+      <c r="J65" s="362" t="n"/>
+      <c r="K65" s="360" t="n"/>
+      <c r="L65" s="362" t="n"/>
     </row>
     <row r="66" ht="18" customHeight="1" s="127">
-      <c r="A66" s="126" t="n">
+      <c r="A66" s="370" t="n">
         <v>20</v>
       </c>
-      <c r="B66" s="76" t="n"/>
-      <c r="C66" s="93" t="n"/>
-      <c r="D66" s="89" t="n"/>
-      <c r="E66" s="76" t="n"/>
-      <c r="F66" s="89" t="n"/>
-      <c r="G66" s="76" t="n"/>
-      <c r="H66" s="89" t="n"/>
-      <c r="I66" s="76" t="n"/>
-      <c r="J66" s="89" t="n"/>
-      <c r="K66" s="76" t="n"/>
-      <c r="L66" s="89" t="n"/>
+      <c r="B66" s="360" t="n"/>
+      <c r="C66" s="361" t="n"/>
+      <c r="D66" s="362" t="n"/>
+      <c r="E66" s="360" t="n"/>
+      <c r="F66" s="362" t="n"/>
+      <c r="G66" s="360" t="n"/>
+      <c r="H66" s="362" t="n"/>
+      <c r="I66" s="360" t="n"/>
+      <c r="J66" s="362" t="n"/>
+      <c r="K66" s="360" t="n"/>
+      <c r="L66" s="362" t="n"/>
     </row>
     <row r="67" ht="18" customHeight="1" s="127">
-      <c r="A67" s="126" t="n">
+      <c r="A67" s="370" t="n">
         <v>21</v>
       </c>
-      <c r="B67" s="76" t="n"/>
-      <c r="C67" s="93" t="n"/>
-      <c r="D67" s="89" t="n"/>
-      <c r="E67" s="76" t="n"/>
-      <c r="F67" s="89" t="n"/>
-      <c r="G67" s="76" t="n"/>
-      <c r="H67" s="89" t="n"/>
-      <c r="I67" s="76" t="n"/>
-      <c r="J67" s="89" t="n"/>
-      <c r="K67" s="76" t="n"/>
-      <c r="L67" s="89" t="n"/>
+      <c r="B67" s="360" t="n"/>
+      <c r="C67" s="361" t="n"/>
+      <c r="D67" s="362" t="n"/>
+      <c r="E67" s="360" t="n"/>
+      <c r="F67" s="362" t="n"/>
+      <c r="G67" s="360" t="n"/>
+      <c r="H67" s="362" t="n"/>
+      <c r="I67" s="360" t="n"/>
+      <c r="J67" s="362" t="n"/>
+      <c r="K67" s="360" t="n"/>
+      <c r="L67" s="362" t="n"/>
     </row>
     <row r="68" ht="18" customHeight="1" s="127">
-      <c r="A68" s="126" t="n">
+      <c r="A68" s="370" t="n">
         <v>22</v>
       </c>
-      <c r="B68" s="76" t="n"/>
-      <c r="C68" s="93" t="n"/>
-      <c r="D68" s="89" t="n"/>
-      <c r="E68" s="76" t="n"/>
-      <c r="F68" s="89" t="n"/>
-      <c r="G68" s="76" t="n"/>
-      <c r="H68" s="89" t="n"/>
-      <c r="I68" s="76" t="n"/>
-      <c r="J68" s="89" t="n"/>
-      <c r="K68" s="76" t="n"/>
-      <c r="L68" s="89" t="n"/>
+      <c r="B68" s="360" t="n"/>
+      <c r="C68" s="361" t="n"/>
+      <c r="D68" s="362" t="n"/>
+      <c r="E68" s="360" t="n"/>
+      <c r="F68" s="362" t="n"/>
+      <c r="G68" s="360" t="n"/>
+      <c r="H68" s="362" t="n"/>
+      <c r="I68" s="360" t="n"/>
+      <c r="J68" s="362" t="n"/>
+      <c r="K68" s="360" t="n"/>
+      <c r="L68" s="362" t="n"/>
     </row>
     <row r="69" ht="18" customHeight="1" s="127">
-      <c r="A69" s="126" t="n">
+      <c r="A69" s="370" t="n">
         <v>23</v>
       </c>
-      <c r="B69" s="76" t="n"/>
-      <c r="C69" s="93" t="n"/>
-      <c r="D69" s="89" t="n"/>
-      <c r="E69" s="76" t="n"/>
-      <c r="F69" s="89" t="n"/>
-      <c r="G69" s="76" t="n"/>
-      <c r="H69" s="89" t="n"/>
-      <c r="I69" s="76" t="n"/>
-      <c r="J69" s="89" t="n"/>
-      <c r="K69" s="76" t="n"/>
-      <c r="L69" s="89" t="n"/>
+      <c r="B69" s="360" t="n"/>
+      <c r="C69" s="361" t="n"/>
+      <c r="D69" s="362" t="n"/>
+      <c r="E69" s="360" t="n"/>
+      <c r="F69" s="362" t="n"/>
+      <c r="G69" s="360" t="n"/>
+      <c r="H69" s="362" t="n"/>
+      <c r="I69" s="360" t="n"/>
+      <c r="J69" s="362" t="n"/>
+      <c r="K69" s="360" t="n"/>
+      <c r="L69" s="362" t="n"/>
     </row>
     <row r="70" ht="18" customHeight="1" s="127">
-      <c r="A70" s="126" t="n">
+      <c r="A70" s="370" t="n">
         <v>24</v>
       </c>
-      <c r="B70" s="76" t="n"/>
-      <c r="C70" s="93" t="n"/>
-      <c r="D70" s="89" t="n"/>
-      <c r="E70" s="76" t="n"/>
-      <c r="F70" s="89" t="n"/>
-      <c r="G70" s="76" t="n"/>
-      <c r="H70" s="89" t="n"/>
-      <c r="I70" s="76" t="n"/>
-      <c r="J70" s="89" t="n"/>
-      <c r="K70" s="76" t="n"/>
-      <c r="L70" s="89" t="n"/>
+      <c r="B70" s="360" t="n"/>
+      <c r="C70" s="361" t="n"/>
+      <c r="D70" s="362" t="n"/>
+      <c r="E70" s="360" t="n"/>
+      <c r="F70" s="362" t="n"/>
+      <c r="G70" s="360" t="n"/>
+      <c r="H70" s="362" t="n"/>
+      <c r="I70" s="360" t="n"/>
+      <c r="J70" s="362" t="n"/>
+      <c r="K70" s="360" t="n"/>
+      <c r="L70" s="362" t="n"/>
     </row>
     <row r="71" ht="18" customHeight="1" s="127">
-      <c r="A71" s="126" t="n">
+      <c r="A71" s="370" t="n">
         <v>25</v>
       </c>
-      <c r="B71" s="76" t="n"/>
-      <c r="C71" s="93" t="n"/>
-      <c r="D71" s="89" t="n"/>
-      <c r="E71" s="76" t="n"/>
-      <c r="F71" s="89" t="n"/>
-      <c r="G71" s="76" t="n"/>
-      <c r="H71" s="89" t="n"/>
-      <c r="I71" s="76" t="n"/>
-      <c r="J71" s="89" t="n"/>
-      <c r="K71" s="76" t="n"/>
-      <c r="L71" s="89" t="n"/>
+      <c r="B71" s="360" t="n"/>
+      <c r="C71" s="361" t="n"/>
+      <c r="D71" s="362" t="n"/>
+      <c r="E71" s="360" t="n"/>
+      <c r="F71" s="362" t="n"/>
+      <c r="G71" s="360" t="n"/>
+      <c r="H71" s="362" t="n"/>
+      <c r="I71" s="360" t="n"/>
+      <c r="J71" s="362" t="n"/>
+      <c r="K71" s="360" t="n"/>
+      <c r="L71" s="362" t="n"/>
     </row>
     <row r="72" ht="18" customHeight="1" s="127">
-      <c r="A72" s="126" t="n">
+      <c r="A72" s="370" t="n">
         <v>26</v>
       </c>
-      <c r="B72" s="76" t="n"/>
-      <c r="C72" s="93" t="n"/>
-      <c r="D72" s="89" t="n"/>
-      <c r="E72" s="76" t="n"/>
-      <c r="F72" s="89" t="n"/>
-      <c r="G72" s="76" t="n"/>
-      <c r="H72" s="89" t="n"/>
-      <c r="I72" s="76" t="n"/>
-      <c r="J72" s="89" t="n"/>
-      <c r="K72" s="76" t="n"/>
-      <c r="L72" s="89" t="n"/>
+      <c r="B72" s="360" t="n"/>
+      <c r="C72" s="361" t="n"/>
+      <c r="D72" s="362" t="n"/>
+      <c r="E72" s="360" t="n"/>
+      <c r="F72" s="362" t="n"/>
+      <c r="G72" s="360" t="n"/>
+      <c r="H72" s="362" t="n"/>
+      <c r="I72" s="360" t="n"/>
+      <c r="J72" s="362" t="n"/>
+      <c r="K72" s="360" t="n"/>
+      <c r="L72" s="362" t="n"/>
     </row>
     <row r="73" ht="18" customHeight="1" s="127">
-      <c r="A73" s="126" t="n">
+      <c r="A73" s="370" t="n">
         <v>27</v>
       </c>
-      <c r="B73" s="76" t="n"/>
-      <c r="C73" s="93" t="n"/>
-      <c r="D73" s="89" t="n"/>
-      <c r="E73" s="76" t="n"/>
-      <c r="F73" s="89" t="n"/>
-      <c r="G73" s="76" t="n"/>
-      <c r="H73" s="89" t="n"/>
-      <c r="I73" s="76" t="n"/>
-      <c r="J73" s="89" t="n"/>
-      <c r="K73" s="76" t="n"/>
-      <c r="L73" s="89" t="n"/>
+      <c r="B73" s="360" t="n"/>
+      <c r="C73" s="361" t="n"/>
+      <c r="D73" s="362" t="n"/>
+      <c r="E73" s="360" t="n"/>
+      <c r="F73" s="362" t="n"/>
+      <c r="G73" s="360" t="n"/>
+      <c r="H73" s="362" t="n"/>
+      <c r="I73" s="360" t="n"/>
+      <c r="J73" s="362" t="n"/>
+      <c r="K73" s="360" t="n"/>
+      <c r="L73" s="362" t="n"/>
     </row>
     <row r="74" ht="18" customHeight="1" s="127">
-      <c r="A74" s="126" t="n">
+      <c r="A74" s="370" t="n">
         <v>28</v>
       </c>
-      <c r="B74" s="76" t="n"/>
-      <c r="C74" s="93" t="n"/>
-      <c r="D74" s="89" t="n"/>
-      <c r="E74" s="76" t="n"/>
-      <c r="F74" s="89" t="n"/>
-      <c r="G74" s="76" t="n"/>
-      <c r="H74" s="89" t="n"/>
-      <c r="I74" s="76" t="n"/>
-      <c r="J74" s="89" t="n"/>
-      <c r="K74" s="76" t="n"/>
-      <c r="L74" s="89" t="n"/>
+      <c r="B74" s="360" t="n"/>
+      <c r="C74" s="361" t="n"/>
+      <c r="D74" s="362" t="n"/>
+      <c r="E74" s="360" t="n"/>
+      <c r="F74" s="362" t="n"/>
+      <c r="G74" s="360" t="n"/>
+      <c r="H74" s="362" t="n"/>
+      <c r="I74" s="360" t="n"/>
+      <c r="J74" s="362" t="n"/>
+      <c r="K74" s="360" t="n"/>
+      <c r="L74" s="362" t="n"/>
     </row>
     <row r="75" ht="18" customHeight="1" s="127">
-      <c r="A75" s="126" t="n">
+      <c r="A75" s="370" t="n">
         <v>29</v>
       </c>
-      <c r="B75" s="76" t="n"/>
-      <c r="C75" s="93" t="n"/>
-      <c r="D75" s="89" t="n"/>
-      <c r="E75" s="76" t="n"/>
-      <c r="F75" s="89" t="n"/>
-      <c r="G75" s="76" t="n"/>
-      <c r="H75" s="89" t="n"/>
-      <c r="I75" s="76" t="n"/>
-      <c r="J75" s="89" t="n"/>
-      <c r="K75" s="76" t="n"/>
-      <c r="L75" s="89" t="n"/>
+      <c r="B75" s="360" t="n"/>
+      <c r="C75" s="361" t="n"/>
+      <c r="D75" s="362" t="n"/>
+      <c r="E75" s="360" t="n"/>
+      <c r="F75" s="362" t="n"/>
+      <c r="G75" s="360" t="n"/>
+      <c r="H75" s="362" t="n"/>
+      <c r="I75" s="360" t="n"/>
+      <c r="J75" s="362" t="n"/>
+      <c r="K75" s="360" t="n"/>
+      <c r="L75" s="362" t="n"/>
     </row>
     <row r="76" ht="18" customHeight="1" s="127">
-      <c r="A76" s="126" t="n">
+      <c r="A76" s="370" t="n">
         <v>30</v>
       </c>
-      <c r="B76" s="76" t="n"/>
-      <c r="C76" s="93" t="n"/>
-      <c r="D76" s="89" t="n"/>
-      <c r="E76" s="76" t="n"/>
-      <c r="F76" s="89" t="n"/>
-      <c r="G76" s="76" t="n"/>
-      <c r="H76" s="89" t="n"/>
-      <c r="I76" s="76" t="n"/>
-      <c r="J76" s="89" t="n"/>
-      <c r="K76" s="76" t="n"/>
-      <c r="L76" s="89" t="n"/>
+      <c r="B76" s="360" t="n"/>
+      <c r="C76" s="361" t="n"/>
+      <c r="D76" s="362" t="n"/>
+      <c r="E76" s="360" t="n"/>
+      <c r="F76" s="362" t="n"/>
+      <c r="G76" s="360" t="n"/>
+      <c r="H76" s="362" t="n"/>
+      <c r="I76" s="360" t="n"/>
+      <c r="J76" s="362" t="n"/>
+      <c r="K76" s="360" t="n"/>
+      <c r="L76" s="362" t="n"/>
     </row>
     <row r="77" ht="21" customHeight="1" s="127">
       <c r="A77" s="226" t="inlineStr">
@@ -3856,116 +3932,228 @@
       <c r="L78" s="89" t="n"/>
     </row>
     <row r="79" ht="16.5" customHeight="1" s="127">
-      <c r="A79" s="129" t="n"/>
-      <c r="B79" s="104" t="n"/>
-      <c r="C79" s="104" t="n"/>
-      <c r="D79" s="104" t="n"/>
-      <c r="E79" s="104" t="n"/>
-      <c r="F79" s="94" t="n"/>
-      <c r="G79" s="129" t="n"/>
-      <c r="H79" s="104" t="n"/>
-      <c r="I79" s="104" t="n"/>
-      <c r="J79" s="104" t="n"/>
-      <c r="K79" s="104" t="n"/>
-      <c r="L79" s="94" t="n"/>
+      <c r="A79" s="371" t="n"/>
+      <c r="B79" s="372" t="n"/>
+      <c r="C79" s="372" t="n"/>
+      <c r="D79" s="372" t="n"/>
+      <c r="E79" s="372" t="n"/>
+      <c r="F79" s="373" t="n"/>
+      <c r="G79" s="371" t="n"/>
+      <c r="H79" s="372" t="n"/>
+      <c r="I79" s="372" t="n"/>
+      <c r="J79" s="372" t="n"/>
+      <c r="K79" s="372" t="n"/>
+      <c r="L79" s="373" t="n"/>
     </row>
     <row r="80" ht="16.5" customHeight="1" s="127">
-      <c r="A80" s="95" t="n"/>
-      <c r="F80" s="92" t="n"/>
-      <c r="G80" s="95" t="n"/>
-      <c r="L80" s="92" t="n"/>
+      <c r="A80" s="374" t="n"/>
+      <c r="B80" s="375" t="n"/>
+      <c r="C80" s="375" t="n"/>
+      <c r="D80" s="375" t="n"/>
+      <c r="E80" s="375" t="n"/>
+      <c r="F80" s="376" t="n"/>
+      <c r="G80" s="374" t="n"/>
+      <c r="H80" s="375" t="n"/>
+      <c r="I80" s="375" t="n"/>
+      <c r="J80" s="375" t="n"/>
+      <c r="K80" s="375" t="n"/>
+      <c r="L80" s="376" t="n"/>
     </row>
     <row r="81" ht="16.5" customHeight="1" s="127">
-      <c r="A81" s="95" t="n"/>
-      <c r="F81" s="92" t="n"/>
-      <c r="G81" s="95" t="n"/>
-      <c r="L81" s="92" t="n"/>
+      <c r="A81" s="374" t="n"/>
+      <c r="B81" s="375" t="n"/>
+      <c r="C81" s="375" t="n"/>
+      <c r="D81" s="375" t="n"/>
+      <c r="E81" s="375" t="n"/>
+      <c r="F81" s="376" t="n"/>
+      <c r="G81" s="374" t="n"/>
+      <c r="H81" s="375" t="n"/>
+      <c r="I81" s="375" t="n"/>
+      <c r="J81" s="375" t="n"/>
+      <c r="K81" s="375" t="n"/>
+      <c r="L81" s="376" t="n"/>
     </row>
     <row r="82" ht="16.5" customHeight="1" s="127">
-      <c r="A82" s="95" t="n"/>
-      <c r="F82" s="92" t="n"/>
-      <c r="G82" s="95" t="n"/>
-      <c r="L82" s="92" t="n"/>
+      <c r="A82" s="374" t="n"/>
+      <c r="B82" s="375" t="n"/>
+      <c r="C82" s="375" t="n"/>
+      <c r="D82" s="375" t="n"/>
+      <c r="E82" s="375" t="n"/>
+      <c r="F82" s="376" t="n"/>
+      <c r="G82" s="374" t="n"/>
+      <c r="H82" s="375" t="n"/>
+      <c r="I82" s="375" t="n"/>
+      <c r="J82" s="375" t="n"/>
+      <c r="K82" s="375" t="n"/>
+      <c r="L82" s="376" t="n"/>
     </row>
     <row r="83" ht="16.5" customHeight="1" s="127">
-      <c r="A83" s="95" t="n"/>
-      <c r="F83" s="92" t="n"/>
-      <c r="G83" s="95" t="n"/>
-      <c r="L83" s="92" t="n"/>
+      <c r="A83" s="374" t="n"/>
+      <c r="B83" s="375" t="n"/>
+      <c r="C83" s="375" t="n"/>
+      <c r="D83" s="375" t="n"/>
+      <c r="E83" s="375" t="n"/>
+      <c r="F83" s="376" t="n"/>
+      <c r="G83" s="374" t="n"/>
+      <c r="H83" s="375" t="n"/>
+      <c r="I83" s="375" t="n"/>
+      <c r="J83" s="375" t="n"/>
+      <c r="K83" s="375" t="n"/>
+      <c r="L83" s="376" t="n"/>
     </row>
     <row r="84" ht="16.5" customHeight="1" s="127">
-      <c r="A84" s="95" t="n"/>
-      <c r="F84" s="92" t="n"/>
-      <c r="G84" s="95" t="n"/>
-      <c r="L84" s="92" t="n"/>
+      <c r="A84" s="374" t="n"/>
+      <c r="B84" s="375" t="n"/>
+      <c r="C84" s="375" t="n"/>
+      <c r="D84" s="375" t="n"/>
+      <c r="E84" s="375" t="n"/>
+      <c r="F84" s="376" t="n"/>
+      <c r="G84" s="374" t="n"/>
+      <c r="H84" s="375" t="n"/>
+      <c r="I84" s="375" t="n"/>
+      <c r="J84" s="375" t="n"/>
+      <c r="K84" s="375" t="n"/>
+      <c r="L84" s="376" t="n"/>
     </row>
     <row r="85" ht="13.5" customHeight="1" s="127">
-      <c r="A85" s="95" t="n"/>
-      <c r="F85" s="92" t="n"/>
-      <c r="G85" s="95" t="n"/>
-      <c r="L85" s="92" t="n"/>
+      <c r="A85" s="374" t="n"/>
+      <c r="B85" s="375" t="n"/>
+      <c r="C85" s="375" t="n"/>
+      <c r="D85" s="375" t="n"/>
+      <c r="E85" s="375" t="n"/>
+      <c r="F85" s="376" t="n"/>
+      <c r="G85" s="374" t="n"/>
+      <c r="H85" s="375" t="n"/>
+      <c r="I85" s="375" t="n"/>
+      <c r="J85" s="375" t="n"/>
+      <c r="K85" s="375" t="n"/>
+      <c r="L85" s="376" t="n"/>
     </row>
     <row r="86" ht="13.5" customHeight="1" s="127">
-      <c r="A86" s="95" t="n"/>
-      <c r="F86" s="92" t="n"/>
-      <c r="G86" s="95" t="n"/>
-      <c r="L86" s="92" t="n"/>
+      <c r="A86" s="374" t="n"/>
+      <c r="B86" s="375" t="n"/>
+      <c r="C86" s="375" t="n"/>
+      <c r="D86" s="375" t="n"/>
+      <c r="E86" s="375" t="n"/>
+      <c r="F86" s="376" t="n"/>
+      <c r="G86" s="374" t="n"/>
+      <c r="H86" s="375" t="n"/>
+      <c r="I86" s="375" t="n"/>
+      <c r="J86" s="375" t="n"/>
+      <c r="K86" s="375" t="n"/>
+      <c r="L86" s="376" t="n"/>
     </row>
     <row r="87" ht="13.5" customHeight="1" s="127">
-      <c r="A87" s="95" t="n"/>
-      <c r="F87" s="92" t="n"/>
-      <c r="G87" s="95" t="n"/>
-      <c r="L87" s="92" t="n"/>
+      <c r="A87" s="374" t="n"/>
+      <c r="B87" s="375" t="n"/>
+      <c r="C87" s="375" t="n"/>
+      <c r="D87" s="375" t="n"/>
+      <c r="E87" s="375" t="n"/>
+      <c r="F87" s="376" t="n"/>
+      <c r="G87" s="374" t="n"/>
+      <c r="H87" s="375" t="n"/>
+      <c r="I87" s="375" t="n"/>
+      <c r="J87" s="375" t="n"/>
+      <c r="K87" s="375" t="n"/>
+      <c r="L87" s="376" t="n"/>
     </row>
     <row r="88" ht="13.5" customHeight="1" s="127">
-      <c r="A88" s="95" t="n"/>
-      <c r="F88" s="92" t="n"/>
-      <c r="G88" s="95" t="n"/>
-      <c r="L88" s="92" t="n"/>
+      <c r="A88" s="374" t="n"/>
+      <c r="B88" s="375" t="n"/>
+      <c r="C88" s="375" t="n"/>
+      <c r="D88" s="375" t="n"/>
+      <c r="E88" s="375" t="n"/>
+      <c r="F88" s="376" t="n"/>
+      <c r="G88" s="374" t="n"/>
+      <c r="H88" s="375" t="n"/>
+      <c r="I88" s="375" t="n"/>
+      <c r="J88" s="375" t="n"/>
+      <c r="K88" s="375" t="n"/>
+      <c r="L88" s="376" t="n"/>
     </row>
     <row r="89" ht="13.5" customHeight="1" s="127">
-      <c r="A89" s="95" t="n"/>
-      <c r="F89" s="92" t="n"/>
-      <c r="G89" s="95" t="n"/>
-      <c r="L89" s="92" t="n"/>
+      <c r="A89" s="374" t="n"/>
+      <c r="B89" s="375" t="n"/>
+      <c r="C89" s="375" t="n"/>
+      <c r="D89" s="375" t="n"/>
+      <c r="E89" s="375" t="n"/>
+      <c r="F89" s="376" t="n"/>
+      <c r="G89" s="374" t="n"/>
+      <c r="H89" s="375" t="n"/>
+      <c r="I89" s="375" t="n"/>
+      <c r="J89" s="375" t="n"/>
+      <c r="K89" s="375" t="n"/>
+      <c r="L89" s="376" t="n"/>
     </row>
     <row r="90" ht="13.5" customHeight="1" s="127">
-      <c r="A90" s="95" t="n"/>
-      <c r="F90" s="92" t="n"/>
-      <c r="G90" s="95" t="n"/>
-      <c r="L90" s="92" t="n"/>
+      <c r="A90" s="374" t="n"/>
+      <c r="B90" s="375" t="n"/>
+      <c r="C90" s="375" t="n"/>
+      <c r="D90" s="375" t="n"/>
+      <c r="E90" s="375" t="n"/>
+      <c r="F90" s="376" t="n"/>
+      <c r="G90" s="374" t="n"/>
+      <c r="H90" s="375" t="n"/>
+      <c r="I90" s="375" t="n"/>
+      <c r="J90" s="375" t="n"/>
+      <c r="K90" s="375" t="n"/>
+      <c r="L90" s="376" t="n"/>
     </row>
     <row r="91" ht="13.5" customHeight="1" s="127">
-      <c r="A91" s="95" t="n"/>
-      <c r="F91" s="92" t="n"/>
-      <c r="G91" s="95" t="n"/>
-      <c r="L91" s="92" t="n"/>
+      <c r="A91" s="374" t="n"/>
+      <c r="B91" s="375" t="n"/>
+      <c r="C91" s="375" t="n"/>
+      <c r="D91" s="375" t="n"/>
+      <c r="E91" s="375" t="n"/>
+      <c r="F91" s="376" t="n"/>
+      <c r="G91" s="374" t="n"/>
+      <c r="H91" s="375" t="n"/>
+      <c r="I91" s="375" t="n"/>
+      <c r="J91" s="375" t="n"/>
+      <c r="K91" s="375" t="n"/>
+      <c r="L91" s="376" t="n"/>
     </row>
     <row r="92" ht="13.5" customHeight="1" s="127">
-      <c r="A92" s="95" t="n"/>
-      <c r="F92" s="92" t="n"/>
-      <c r="G92" s="95" t="n"/>
-      <c r="L92" s="92" t="n"/>
+      <c r="A92" s="374" t="n"/>
+      <c r="B92" s="375" t="n"/>
+      <c r="C92" s="375" t="n"/>
+      <c r="D92" s="375" t="n"/>
+      <c r="E92" s="375" t="n"/>
+      <c r="F92" s="376" t="n"/>
+      <c r="G92" s="374" t="n"/>
+      <c r="H92" s="375" t="n"/>
+      <c r="I92" s="375" t="n"/>
+      <c r="J92" s="375" t="n"/>
+      <c r="K92" s="375" t="n"/>
+      <c r="L92" s="376" t="n"/>
     </row>
     <row r="93" ht="13.5" customHeight="1" s="127">
-      <c r="A93" s="95" t="n"/>
-      <c r="F93" s="92" t="n"/>
-      <c r="G93" s="95" t="n"/>
-      <c r="L93" s="92" t="n"/>
+      <c r="A93" s="374" t="n"/>
+      <c r="B93" s="375" t="n"/>
+      <c r="C93" s="375" t="n"/>
+      <c r="D93" s="375" t="n"/>
+      <c r="E93" s="375" t="n"/>
+      <c r="F93" s="376" t="n"/>
+      <c r="G93" s="374" t="n"/>
+      <c r="H93" s="375" t="n"/>
+      <c r="I93" s="375" t="n"/>
+      <c r="J93" s="375" t="n"/>
+      <c r="K93" s="375" t="n"/>
+      <c r="L93" s="376" t="n"/>
     </row>
     <row r="94" ht="13.5" customHeight="1" s="127">
-      <c r="A94" s="96" t="n"/>
-      <c r="B94" s="98" t="n"/>
-      <c r="C94" s="98" t="n"/>
-      <c r="D94" s="98" t="n"/>
-      <c r="E94" s="98" t="n"/>
-      <c r="F94" s="97" t="n"/>
-      <c r="G94" s="96" t="n"/>
-      <c r="H94" s="98" t="n"/>
-      <c r="I94" s="98" t="n"/>
-      <c r="J94" s="98" t="n"/>
-      <c r="K94" s="98" t="n"/>
-      <c r="L94" s="97" t="n"/>
+      <c r="A94" s="377" t="n"/>
+      <c r="B94" s="368" t="n"/>
+      <c r="C94" s="368" t="n"/>
+      <c r="D94" s="368" t="n"/>
+      <c r="E94" s="368" t="n"/>
+      <c r="F94" s="369" t="n"/>
+      <c r="G94" s="377" t="n"/>
+      <c r="H94" s="368" t="n"/>
+      <c r="I94" s="368" t="n"/>
+      <c r="J94" s="368" t="n"/>
+      <c r="K94" s="368" t="n"/>
+      <c r="L94" s="369" t="n"/>
     </row>
     <row r="95" ht="16.5" customHeight="1" s="127">
       <c r="A95" s="87" t="n"/>
@@ -4028,20 +4216,20 @@
         </is>
       </c>
       <c r="B98" s="97" t="n"/>
-      <c r="C98" s="301" t="n"/>
-      <c r="D98" s="98" t="n"/>
-      <c r="E98" s="98" t="n"/>
-      <c r="F98" s="97" t="n"/>
+      <c r="C98" s="367" t="n"/>
+      <c r="D98" s="368" t="n"/>
+      <c r="E98" s="368" t="n"/>
+      <c r="F98" s="369" t="n"/>
       <c r="G98" s="302" t="inlineStr">
         <is>
           <t>Firma:</t>
         </is>
       </c>
       <c r="H98" s="97" t="n"/>
-      <c r="I98" s="301" t="n"/>
-      <c r="J98" s="98" t="n"/>
-      <c r="K98" s="98" t="n"/>
-      <c r="L98" s="97" t="n"/>
+      <c r="I98" s="367" t="n"/>
+      <c r="J98" s="368" t="n"/>
+      <c r="K98" s="368" t="n"/>
+      <c r="L98" s="369" t="n"/>
     </row>
     <row r="99" ht="21" customHeight="1" s="127">
       <c r="A99" s="70" t="inlineStr">
@@ -4050,20 +4238,20 @@
         </is>
       </c>
       <c r="B99" s="89" t="n"/>
-      <c r="C99" s="68" t="n"/>
-      <c r="D99" s="93" t="n"/>
-      <c r="E99" s="93" t="n"/>
-      <c r="F99" s="89" t="n"/>
+      <c r="C99" s="360" t="n"/>
+      <c r="D99" s="361" t="n"/>
+      <c r="E99" s="361" t="n"/>
+      <c r="F99" s="362" t="n"/>
       <c r="G99" s="70" t="inlineStr">
         <is>
           <t>Nombre:</t>
         </is>
       </c>
       <c r="H99" s="89" t="n"/>
-      <c r="I99" s="68" t="n"/>
-      <c r="J99" s="93" t="n"/>
-      <c r="K99" s="93" t="n"/>
-      <c r="L99" s="89" t="n"/>
+      <c r="I99" s="360" t="n"/>
+      <c r="J99" s="361" t="n"/>
+      <c r="K99" s="361" t="n"/>
+      <c r="L99" s="362" t="n"/>
     </row>
     <row r="100" ht="21" customHeight="1" s="127">
       <c r="A100" s="70" t="inlineStr">
@@ -4072,20 +4260,20 @@
         </is>
       </c>
       <c r="B100" s="89" t="n"/>
-      <c r="C100" s="68" t="n"/>
-      <c r="D100" s="93" t="n"/>
-      <c r="E100" s="93" t="n"/>
-      <c r="F100" s="89" t="n"/>
+      <c r="C100" s="360" t="n"/>
+      <c r="D100" s="361" t="n"/>
+      <c r="E100" s="361" t="n"/>
+      <c r="F100" s="362" t="n"/>
       <c r="G100" s="70" t="inlineStr">
         <is>
           <t>Cargo:</t>
         </is>
       </c>
       <c r="H100" s="89" t="n"/>
-      <c r="I100" s="68" t="n"/>
-      <c r="J100" s="93" t="n"/>
-      <c r="K100" s="93" t="n"/>
-      <c r="L100" s="89" t="n"/>
+      <c r="I100" s="360" t="n"/>
+      <c r="J100" s="361" t="n"/>
+      <c r="K100" s="361" t="n"/>
+      <c r="L100" s="362" t="n"/>
     </row>
     <row r="101">
       <c r="A101" s="19" t="inlineStr">
@@ -4104,6 +4292,7 @@
       </c>
     </row>
   </sheetData>
+  <sheetProtection selectLockedCells="0" selectUnlockedCells="0" sheet="1" objects="0" insertRows="1" insertHyperlinks="1" autoFilter="1" scenarios="0" formatColumns="0" deleteColumns="1" insertColumns="1" pivotTables="1" deleteRows="1" formatCells="1" formatRows="0" sort="1"/>
   <mergeCells count="265">
     <mergeCell ref="G38:I38"/>
     <mergeCell ref="K49:L49"/>
